--- a/static/standards-correlations/Tennessee_CS1_State_Standards.xlsx
+++ b/static/standards-correlations/Tennessee_CS1_State_Standards.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Crosswalk" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Legend &amp; Attribution" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Crosswalk" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Legend &amp; Attribution" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Crosswalk'!$A$4:$I$29</definedName>
@@ -565,10 +565,11 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Scored against full lab bodies | C and Python tracks | Discovery Projects | TN high school band, CS graduation-requirement course (NOT AP, IB, dual enrollment, or CTE IT)</t>
-        </is>
-      </c>
-    </row>
+          <t>Scored against full lab bodies | C and Python tracks | Introductory Projects | TN high school band, CS graduation-requirement course (NOT AP, IB, dual enrollment, or CTE IT)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
     <row r="4" ht="32" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -602,7 +603,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>Discovery Projects</t>
+          <t>Introductory Projects</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
@@ -1563,7 +1564,7 @@
       </c>
       <c r="I25" s="5" t="inlineStr">
         <is>
-          <t>Unit 1.1 carries 'use a structured debugging process to find and fix errors in your code' as a stated objective, and its reflection requires describing a specific bug by symptom, cause, and fix - which is the two-step identify-then-fix shape Tennessee asks for. Units 1.3, 1.4, 1.5, and 2.3 each carry a dedicated common-bugs callout naming the failure modes of that construct. Loop debugging specifically appears in Unit 2.3 (clear before read) and Unit 5.4 (walking a nested sort by hand). Discovery Coding 2 notes professionals spend most of their time debugging.</t>
+          <t>Unit 1.1 carries 'use a structured debugging process to find and fix errors in your code' as a stated objective, and its reflection requires describing a specific bug by symptom, cause, and fix - which is the two-step identify-then-fix shape Tennessee asks for. Units 1.3, 1.4, 1.5, and 2.3 each carry a dedicated common-bugs callout naming the failure modes of that construct. Loop debugging specifically appears in Unit 2.3 (clear before read) and Unit 5.4 (walking a nested sort by hand). Introductory Coding 2 notes professionals spend most of their time debugging.</t>
         </is>
       </c>
     </row>
@@ -1769,6 +1770,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="14" t="inlineStr">
         <is>
@@ -1813,7 +1815,7 @@
       </c>
       <c r="B6" s="15" t="inlineStr">
         <is>
-          <t>Discovery Project, Coding strand, project NN (01-17).</t>
+          <t>Introductory Project, Coding strand, project NN (01-17).</t>
         </is>
       </c>
     </row>
@@ -1825,7 +1827,7 @@
       </c>
       <c r="B7" s="15" t="inlineStr">
         <is>
-          <t>Discovery Project, Systems strand, project NN (01-14).</t>
+          <t>Introductory Project, Systems strand, project NN (01-14).</t>
         </is>
       </c>
     </row>
@@ -1949,6 +1951,8 @@
         </is>
       </c>
     </row>
+    <row r="18"/>
+    <row r="19"/>
     <row r="20">
       <c r="A20" s="13" t="inlineStr">
         <is>
@@ -1977,7 +1981,7 @@
 - Computer Science FAQ: graduation requirement mechanics and the special course application.
 Crosswalk analysis (c) KIPR / Botball Explorer.
 === METHODOLOGY (revised) ===
-Scored against FULL LAB BODIES: reflection prompts, Individual Reflection phases, AI Literacy Bridge sections, and Extension Challenges. Evidence base is 750 reflection prompts and 255 Extension Challenges across 27 C labs, 27 Python labs, and 31 Discovery projects.
+Scored against FULL LAB BODIES: reflection prompts, Individual Reflection phases, AI Literacy Bridge sections, and Extension Challenges. Evidence base is 750 reflection prompts and 255 Extension Challenges across 27 C labs, 27 Python labs, and 31 Introductory projects.
 Scoring rule: Full requires evidence in the core lab flow. Partial is assigned where the only evidence sits in an optional Extension Challenge (labelled 'Finished early?'), or where the standard is only partly met.
 RESULT SHAPE - READ BEFORE PRESENTING: 11 Full, 12 Partial, 2 blank of 25. Touched 23 of 25.
 This is a PARTIAL-HEAVY file and the reason is structural, not a weakness spread evenly through the curriculum. Tennessee devotes 7 of its 25 high school standards - 28 percent - to Networking and the Internet, and writes that strand around cybersecurity, digital citizenship, user tracking, and end-user agreements. Six of those seven score Partial and one is blank. Read the file by strand:
